--- a/बजेट माग estimate/thekka/ओडारे सिंचाई/ओडारे सिंचाई - sir.xlsx
+++ b/बजेट माग estimate/thekka/ओडारे सिंचाई/ओडारे सिंचाई - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B47EB1-5DC3-4019-B581-4AC11C918174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC485B8-12BA-4254-942B-24AA514B312D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -126,18 +126,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
@@ -145,9 +133,6 @@
   </si>
   <si>
     <t>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</t>
-  </si>
-  <si>
-    <t>User contribution</t>
   </si>
   <si>
     <t>Location:- Shankharapur Municipality 1</t>
@@ -255,6 +240,12 @@
   </si>
   <si>
     <t>For irrigation works</t>
+  </si>
+  <si>
+    <t>VAT 13%</t>
+  </si>
+  <si>
+    <t>Grand total</t>
   </si>
 </sst>
 </file>
@@ -430,7 +421,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -545,24 +536,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,8 +552,23 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1108,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -1127,113 +1115,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="A6" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
+      <c r="H6" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
+      <c r="A7" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="H7" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1272,10 +1260,10 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" s="12"/>
       <c r="D9" s="14"/>
@@ -1292,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -1307,7 +1295,7 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" s="37">
         <v>0.5</v>
@@ -1389,7 +1377,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -1479,7 +1467,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -1528,7 +1516,7 @@
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C20" s="17">
         <f>C19</f>
@@ -1602,7 +1590,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -1689,10 +1677,10 @@
     </row>
     <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="14"/>
@@ -1709,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1737,7 +1725,7 @@
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="32" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C29" s="17">
         <v>1</v>
@@ -1763,7 +1751,7 @@
     <row r="30" spans="1:25" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
@@ -1774,7 +1762,7 @@
         <v>18.5625</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I30" s="6">
         <f>1.15*748.9</f>
@@ -1817,7 +1805,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -1845,7 +1833,7 @@
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="32" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C33" s="17">
         <f>C29</f>
@@ -1869,7 +1857,7 @@
     <row r="34" spans="1:25" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="4"/>
@@ -1880,7 +1868,7 @@
         <v>275</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I34" s="6">
         <f>1.15*6461.51/1000</f>
@@ -1936,17 +1924,17 @@
         <v>7</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="42" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G36" s="17"/>
       <c r="H36" s="17"/>
@@ -1957,7 +1945,7 @@
     <row r="37" spans="1:25" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="43" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C37" s="27">
         <f>C33</f>
@@ -2010,7 +1998,7 @@
         <v>222.20000000000002</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I38" s="6">
         <v>287</v>
@@ -2039,7 +2027,7 @@
         <v>8</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -2054,7 +2042,7 @@
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="32" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C41" s="17">
         <v>1</v>
@@ -2076,7 +2064,7 @@
     <row r="42" spans="1:25" s="45" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
@@ -2087,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I42" s="6">
         <v>777</v>
@@ -2116,7 +2104,7 @@
         <v>9</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -2129,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I44" s="6">
         <v>5000</v>
@@ -2240,14 +2228,12 @@
       <c r="B50" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="52">
+      <c r="C50" s="46">
         <f>J48</f>
         <v>313280.68955717236</v>
       </c>
-      <c r="D50" s="53"/>
-      <c r="E50" s="9">
-        <v>100</v>
-      </c>
+      <c r="D50" s="47"/>
+      <c r="E50" s="9"/>
       <c r="F50" s="26"/>
       <c r="G50" s="28"/>
       <c r="H50" s="26"/>
@@ -2264,78 +2250,28 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B51" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="56">
-        <v>275000</v>
-      </c>
-      <c r="D51" s="57"/>
+        <v>51</v>
+      </c>
+      <c r="C51" s="50">
+        <f>13%*C50</f>
+        <v>40726.489642432411</v>
+      </c>
+      <c r="D51" s="51"/>
       <c r="E51" s="9"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B52" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="56">
-        <f>C51-C54-C55</f>
-        <v>261250</v>
-      </c>
-      <c r="D52" s="57"/>
-      <c r="E52" s="9">
-        <f>C52/C50*100</f>
-        <v>83.391670380093132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B53" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="58">
-        <f>C50-C52</f>
-        <v>52030.689557172358</v>
-      </c>
-      <c r="D53" s="58"/>
-      <c r="E53" s="9">
-        <f>100-E52</f>
-        <v>16.608329619906868</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B54" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="52">
-        <f>C51*0.03</f>
-        <v>8250</v>
-      </c>
-      <c r="D54" s="53"/>
-      <c r="E54" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B55" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="52">
-        <f>C51*0.02</f>
-        <v>5500</v>
-      </c>
-      <c r="D55" s="53"/>
-      <c r="E55" s="9">
-        <v>2</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C52" s="50">
+        <f>SUM(C50:D51)</f>
+        <v>354007.17919960478</v>
+      </c>
+      <c r="D52" s="51"/>
+      <c r="E52" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
+  <mergeCells count="12">
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2343,6 +2279,11 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
